--- a/docs/06-bom/最终采购BOM-三板合并.xlsx
+++ b/docs/06-bom/最终采购BOM-三板合并.xlsx
@@ -10,9 +10,13 @@
     <sheet name="最终采购BOM" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="合并决策" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="下单必读与待核实" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="机箱件清单" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="核对记录" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'最终采购BOM'!$A$1:$O$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'机箱件清单'!$A$1:$F$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'核对记录'!$A$1:$D$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,7 +54,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B3F00"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -132,6 +141,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5992,4 +6010,756 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="86" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>规格 / 依据</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>🔴 下单要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>高频变压器 TR_LOW</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>定制</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>四抽头 7.07 / 12.25 / 22.36 / 38.73 Vrms（相对 com）；初级 14.1 Vrms / 3.5 Arms；初次级 &gt;4 kV AC/min；环氧真空灌封</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>🔴 加 T-1（磁芯引 PE 线或预留与磁芯导通的 M4 接地螺柱）+ 🔴🔴 T-3（绕组热点内埋 NC 温度开关，引两线）。🔴 卡下单的一问：频率范围是否覆盖 2–10 kHz。🔴 待决 #70：「7.07 V/7.07 A 是空载抽头电压还是负载端电压？有没有 ≥25% 余量不饱和？」🔴 还要 L_p ≥3.2 mH @2kHz、L_k ≤50 µH @10kHz（两条互相打架，下单前必须谈）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>高频变压器 TR_HIGH</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>定制</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>三抽头 70.7 / 122.5 / 223.6 Vrms；初级同 TR_LOW；匝比正好是 TR_LOW 的 10.00 倍</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>同上。🔴 223.6 Vrms 是全机最高电压</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>KSAFE 安全切断继电器 G7L-2A-BUBJ DC12</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>继电器</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>接点 25 A / 250 VAC；线圈 158 mA / 75 Ω / 1.90 W；线圈↔接点 4000 VAC + 冲击 10 kV；动作·释放 ≤30 ms</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 **两只串联、每只用满两个极**：一个极切 `OUT_SEL`、另一个极切 `TR_COM`（双极断开 + 串联冗余）。🔴 线圈**不接 MCU**，由机箱互锁链直接供电。🟢 续流二极管**不用另买** —— 已在 RLY-01 板上（`D1` 1N4007W），`P1.2`/`P1.3` 正好是线圈两端</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>门互锁行程开关</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>开关</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>常闭 NC</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>🔴 硬串进 KSAFE 的 12 V 线圈回路（不只是给 TCA9539 看）。断开延时 = 机械 ≤30 ms + 续流 9.36 ms ≈ 39 ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>DRS-240-36</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>导轨模块</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>DC-UPS 240 W / 36 V；Vboost 43.2 / Vfloat 41.4 V；AC 1.4 A@230V；冷启动浪涌 60 A；支持锂铁曲线</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>🔴 `CN1` 上的 `RTH+/RTH−`（电池 NTC）和 `Force Button`（电池冷启动）**必须引到机箱/面板**。🟡 内置 MODBus(RJ45) 可读电池状态（可能替代待决 #7）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>DDR-30L-12</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>导轨模块</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>36 V → 12 V DC/DC</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>🔴 共模尖峰 0.36 A 要经 MAIN-01 星点 `R16` 闭环 → 线束端子簇要紧挨星点</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>DDR-30L-5</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>导轨模块</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>36 V → 5 V DC/DC</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>电池包 + BMS</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>LiFePO₄，续航 ≈4.6 h（指标 ≥2 h）</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>ADR-007 外购件。🔴 `BAT_OK` 对 LiFePO₄ 只有约 3 分钟预警（33 V 报警 ↔ 31.3 V 切断，只差 1% 容量）。🟡 待决 #7：要不要选配 UART</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>功放模块（晒邦 TPA3255 600W）</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>BTL，额定负载 4 Ω（我们反射阻抗 4.03 Ω ✅）；输出 49.3 W，余量 3×</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>🔴 板载「低音炮/全频」开关**必须打全频**（低音炮档 95 Hz 低通，2–10 kHz 全被滤掉）。🟡 模块标称 DC30–42 V，只有 boost 末期掉电切换会到 43.2 V</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>DWIN 屏</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>串口屏，接 MAIN-01 `U29`(HY2.0-8P)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>🟡 **12 V 还是 5 V 待核实**；🟡 `U29` 的 3/6 脚悬空、DWIN 脚定义待核实（待决 #63）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>NTC 温度探头</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>传感器</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>M4 环形端子式；🔴 **10 kΩ@25 °C** / B3950 / ±1% / XH2.54-2P 出线 / 0.5~1 m / 耐温 ≥105 °C</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>🔴 阻值必须 10 kΩ（板上 22 kΩ 上拉是按它配的）。🔴🔴 变压器上那两只**必须装磁芯或骨架固定件，绝不贴绕组引出线**；🔴 **磁芯必须接 PE，这条线要画进装配图**（1 kΩ 串阻挡不住 224 mA）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>旋转编码器 EC11</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>面板</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>增量式带定位 + 带按键</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>🔴 **脉冲数 = 定位数**（20/20 或 24/24）。**千万别买「15 脉冲/30 定位」** —— 一半定位点停在 A/B 中间态，手一抖就来回计数</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>面板开关 / 按键</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>面板</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>TCA9539 的 8 路输入：`CC/VA` 模式 · `2/5/8/10 kHz` 四个频率预设 · `Encoder ENTER` · `SYSTEM ENABLE` · `门互锁监视`</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>🟡 具体形式（按键/拨码/旋钮）**待定**，板上每路已配 10 kΩ 上拉 + 100 nF 消抖</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>输出端 GDT</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>保护</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Bourns 600 V 差模</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>🟢 **不上 PCB**（动作时几百安培），放输出端子/机箱侧</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>220 V 强电段</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>强电</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>AC 插座 / 开关 / 保险丝 / 压敏 / EMI 滤波</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>ADR-002 方案 A：**全部机箱件，不上 PCB、不进原理图**。🟡 待决 #1：是否按 ADR-005 换成 IEC C14 三合一模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>尼龙柱 + 螺钉</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>M3，三块板共 15 个安装孔（MAIN-01 6 / RLY-01 5 / SNS-01 4），全部 NPTH</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>🔴 **默认全尼龙柱**。MAIN-01 要接机箱 PE 只能用 `GND` 区那几个孔（H1/H3/H5/H6），H2/H4 必须尼龙。🔴 SNS-01 的 `RS1` 两颗 M3 在带电侧，绝不能金属柱。🔴 **装配文件要写明哪几颗尼龙、哪一颗金属接 PE** —— 这是 ADR-004 唯一的保证</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>线束</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>线材</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>`CN4` 两对绞线 + 总屏蔽（🔴 屏蔽只在主板端接 `AGND`）；`CN2.3/.4` 绞一对到 RLY-01；`CN6/7/8` 三对各自绞；`P1` 三根到机箱互锁链</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>🔴 `P1` 三根线的走向必须画死：`P1.1`=12V→互锁链上游，链下游→线圈→`P1.2`(COIL_LOOP)，线圈另一端→`P1.3`(DGND)。接反了 `D1` 就跑到互锁触点外面，续流失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>机箱 / 面板 / 散热</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>结构</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>🔴 `C34` φ13×**25 mm 高**，先量机箱内高；`C33` 22 mm 直插装在底面 → 背面要留 ≥6 mm 净空</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>🔴 莲花座 `U31` 穿面板**必须用绝缘型**（外壳 = `AMP_GND`，碰机箱就给 `AGND` 加了第二个接地点，破 ADR-004）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F19"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="96" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>核对项</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>方法</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>位号回归：源 BOM ↔ 最终 BOM</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>逐位号集合比对（Counter 差集）</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>✅ MAIN-01 210/210 · RLY-01 36/36 · SNS-01 65/65，**总 311/311**。缺失 0、多出 0、重复 0，**值一个没改**</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>PCB 实际贴装 ↔ BOM</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>拿 Gerber 的 FlyingProbeTesting 元件表和 BOM 位号对比</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>✅ RLY-01 36/36、SNS-01 65/65 真实元件全在 BOM 里；"PCB 上多出来"的 112 / 185 个全是 `PADxxx`（铺铜连接焊盘，不是元件）。反向也没有"BOM 有、板上没有"的</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>MAIN-01 BOM ↔ rev22 网表</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>逐位号比对</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>✅ 只多出 `C75` `C76` `R54` `R65` `SCREW5` `SCREW6`（= `HARD_OK_MON` 链补回 + 六孔到齐），**删除 0 个**。🔴 但 MAIN-01 这次没传 Gerber，**贴装侧没法核**</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>位号跳号（跳号常意味着某件被排除出 BOM）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>按前缀扫连续性</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>✅ 全部查清，没有一个是漏掉的元件：MAIN-01 `CN5`（审图 #28 已删，DDS 只走莲花座）、`U30`（重编号留空）；RLY-01 `U5/U8~U11`（端子编号留空）；SNS-01 `CN5~CN8`(为对齐 MAIN-01 的 CN4/CN9 故意跳)、`U7~U29`（已知跳号）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>合并公式</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>独立用 Python 重算一遍并比对公式引用区域</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>✅ 91 行的三个分板数量、总数量 SUM、+20% ROUNDUP、位号串长度全部对上</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>🔴 跨板同名位号</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>三块板各自从 U1/R1/C1 起号 → 必然撞名</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>🔴 **53 个位号同名不同物**（例：`C1` = MAIN 4.7µF / RLY 100µF / SNS 100nF；`D1` = MAIN 1N4148W / RLY 1N4007W；`U4` = MAIN KF301 / RLY KF301 / SNS AMC3301）。本表按板分列所以不会错，**但贴片/打标/领料时一定要带板名**</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>🟡 本表覆盖范围</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>本表 = **三块 PCB 上的件**。整机还要的机箱件见「机箱件清单」表（18 项）。🟡 两处旧文档已过时：`PCB阶段检查清单.md §六` 里的「蜂鸣器」其实在板上（MAIN-01 `BUZZER1`）、「thermostat ×3」已被 T-3 取代（待决 #57 结案）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/06-bom/最终采购BOM-三板合并.xlsx
+++ b/docs/06-bom/最终采购BOM-三板合并.xlsx
@@ -5656,7 +5656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>OUT_SEL ↔ TAP_3R **1.080 mm @223.6 Vrms**、OUT_SEL ↔ TAP_300R 1.537 mm @101 V。顶层已经改好了（0.520 → 4.020 mm），底层这两段没跟着改。见审图 #36</t>
+          <t>v6 不但没改还退步了：OUT_SEL ↔ TAP_3R 由 1.080 退到 0.400 mm @223.6 Vrms（位置 22.2,−21.4，离 K2.3 1.56 mm）、↔ TAP_300R 1.537→1.209、↔ TR_COM 1.560。判据 2.5 mm。🔴 0.400 mm 已无工艺余量，且正落在待决 #71 那条「硬件 OC 看不见」的环路上。改法：L4 上 OUT_SEL 别出现在 y −16~−26 这条带里，两段本地改道即可。🔴 三块板一起下单，现在就卡这一条。</t>
         </is>
       </c>
     </row>
@@ -5758,12 +5758,12 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>🟡 HV_GND 顶层铺铜碎成 15 块</t>
+          <t>🟡 HV_GND 顶层铺铜碎成 16 块</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>已验证 15 块**每块都有过孔并到底层那块 2835.9 mm² 整铜**，电气上仍是一个整体 ✅。🟡 但其中 6 块只有 1 只过孔 —— 建议每块补到 2 只（一只开路那块就悬空了，而它是四颗隔离芯片的参考地）</t>
+          <t>v4 已补 36 只缝合过孔：三块主铺铜由 26/7/10 只变成 31/26/22 只 ✅ 高压参考地确实是一整块低阻平面。🟡 剩下 13 个小岛（0.29~6.19 mm²）仍各只有 1 只过孔 —— HV_GND 只走 ≈15 mA 直流、单只过孔 1.15 mΩ = 17 µV，电气上无所谓，风险只是单点开路（飞针会抓）。不挡下单，下一版各补第二只（待决 #94）。</t>
         </is>
       </c>
     </row>
@@ -5798,12 +5798,12 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>🔴 这次没有上传 Gerber，两条必改无法复核</t>
+          <t>✅ MAIN-01 v8 已复核，两条必改闭环</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>① 原理图补 U27.5→AGND、U27.6↔U27.7（🔴🔴 顺序：先改原理图再点「导入更新」，反了会清掉 PCB 上已画好的手工连接）② 六个安装孔 φ3.2 改 NPTH。🟢 但从 BOM 位号差异能看出 R54/R65/C75/C76 已补齐（HARD_OK_MON 那条链回来了）、SCREW5/SCREW6 已加</t>
+          <t>审图 #38：6 个 Top→Inner2 盲孔全部改成普通通孔（钻孔文件里再没有任何 Top_to_Inner/Inner_to_*）；六个 φ3.2 安装孔全部进 NPTH（SCREW5/SCREW6 闭环）。L2 三块地 GND 9618 / DGND 5183 / AGND 2901 mm² 与 v7 一模一样，位号 210/210 未变 → 本 BOM 仍然有效，不用重做。🟢 MAIN-01 现在可以下单。</t>
         </is>
       </c>
     </row>
@@ -6004,6 +6004,46 @@
       <c r="D17" s="12" t="inlineStr">
         <is>
           <t>本表的「值/型号」直接取自立创导出的 Comment 列。🟡 **LCSC 编号没有填** —— 项目约定不凭记忆写编号。🟡 高精度那几行（±0.1% 薄膜 51k/806Ω、C0G）下单时按规格挑，不要用立创基础库自动匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="95" customHeight="1">
+      <c r="A18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>SNS-01</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>🔴🔴 测量分压链下臂：806 Ω 和 576 Ω 各买 10 只</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>STM32 差分 ADC 的满量程映射（码 0 对应 −V_REF/2 还是 −V_REF）一直没查实（待决 #93，要查 RM0440 或首板实测）。若是 ±V_REF/2 = ±1.45 V，则 223.6 Vrms 时电压通道占 98.3%，几乎顶格，硬件 OV 跳闸点 288 Vrms 直接削平；若是 ±2.9 V 则只占 49.1%，无需改动。✅ 补救只换这一只电阻、不动 PCB：806 Ω → 576 Ω（E96），分压比 443.9 → 620.8:1，占用降到 70.3%。🟢 两只 ±0.1% 薄膜 ≤25 ppm 电阻，几块钱 —— 各买 10 只，查实后再决定装哪只。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="95" customHeight="1">
+      <c r="A19" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>MAIN-01</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>🔴 六个安装孔全部 NPTH → PE 要另找落点</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>v8 已把六个 φ3.2 全部改成非金属化孔（NPTH），这是最干净的做法 —— 金属柱也接不到铜，ADR-004 的单点接地不可能被破坏。🔴 代价：MAIN-01 上从此没有任何可接机箱 PE 的落点。装配文件必须写死：① 六颗全部尼龙柱；② 机箱 PE 另加一副接 GND 的螺钉端子，或只接机箱本体 + 变压器磁芯（磁芯接 PE 本来就要画进装配图）。🟡 六个 NPTH 位置上四层还留着 φ3.20 零环宽焊盘，钻完正好被钻掉，厂家若问询答「可以整体去掉」。</t>
         </is>
       </c>
     </row>

--- a/docs/06-bom/最终采购BOM-三板合并.xlsx
+++ b/docs/06-bom/最终采购BOM-三板合并.xlsx
@@ -1100,7 +1100,7 @@
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="M11" s="4" t="n"/>
@@ -5272,6 +5272,7 @@
         </is>
       </c>
     </row>
+    <row r="93"/>
     <row r="94">
       <c r="C94" s="10" t="inlineStr">
         <is>
@@ -5656,7 +5657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5718,12 +5719,12 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>🔴 L4 还剩两处功能绝缘间距</t>
+          <t>🟡 RLY-01 v7：最危险那条解决了，还剩五笔</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>v6 不但没改还退步了：OUT_SEL ↔ TAP_3R 由 1.080 退到 0.400 mm @223.6 Vrms（位置 22.2,−21.4，离 K2.3 1.56 mm）、↔ TAP_300R 1.537→1.209、↔ TR_COM 1.560。判据 2.5 mm。🔴 0.400 mm 已无工艺余量，且正落在待决 #71 那条「硬件 OC 看不见」的环路上。改法：L4 上 OUT_SEL 别出现在 y −16~−26 这条带里，两段本地改道即可。🔴 三块板一起下单，现在就卡这一条。</t>
+          <t>v7 把 L4 的 OUT_SEL↔TAP_3R 从 0.400 改到 2.040 mm（5.1×）✅，TAP_1R 还改成了顶底同形+28 只缝合过孔（ΔT 14.4→8.7 °C）✅。🔴 还差：① OUT_SEL 有效线宽 2.48 mm / ΔT 26.3 °C（v6 就掉的，需 2.93）② L4 OUT_SEL↔TAP_300R 1.209 ③ ↔TR_COM 1.560 ④ ↔TAP_3R 2.040 ⑤ ↔TAP_10R 2.360（判据 2.5，只算 223.6 Vrms 的对）。🟢 不会打火（最紧 262 V/mm vs 3 kV/mm，余量 11.5×），是爬电碳化+认证问题。都是本地改道，半小时。三板一起下单就卡这一条。</t>
         </is>
       </c>
     </row>
@@ -6044,6 +6045,46 @@
       <c r="D19" s="12" t="inlineStr">
         <is>
           <t>v8 已把六个 φ3.2 全部改成非金属化孔（NPTH），这是最干净的做法 —— 金属柱也接不到铜，ADR-004 的单点接地不可能被破坏。🔴 代价：MAIN-01 上从此没有任何可接机箱 PE 的落点。装配文件必须写死：① 六颗全部尼龙柱；② 机箱 PE 另加一副接 GND 的螺钉端子，或只接机箱本体 + 变压器磁芯（磁芯接 PE 本来就要画进装配图）。🟡 六个 NPTH 位置上四层还留着 φ3.20 零环宽焊盘，钻完正好被钻掉，厂家若问询答「可以整体去掉」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="95" customHeight="1">
+      <c r="A20" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>RLY-01</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>🟡 板框由 150×90 改成 150×100 mm</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>v6 起板框 Y 由 −88.22~+1.78 变成 −88.22~+11.78，多出来的 10 mm 顶边几乎全给了 L4 上一块 513.7 mm² 的 TR_COM 铺铜（这正是 TR_COM 能拿到 3.14 mm / ΔT 17.8 °C 的原因）。🔴 机箱/面板开孔图、装配图的板尺寸、打样报价都要跟着改（90→100 mm 跨了常见尺寸档）。🟡 五个安装孔坐标没变，最上面两个仍在 Y=−20 → 拧顶边端子螺钉时板底仍需垫一下。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="95" customHeight="1">
+      <c r="A21" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>RLY-01</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>🔴 驱动 IC 位号 U1 → U5，本表要同步改</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>v7 把 18 脚达林顿阵列（ULN2803A / TBD62083A）的位号从 U1 改成 U5，位置、角度、18 个脚的网络一字未改，纯改号。🔴 本 BOM 里那一行写的还是 U1，备料前必须改成 U5。🟡 待决 #84 仍未定：ULN2803A 还是 TBD62083A —— 引脚兼容，压降 1.1 V vs 44 mV，线圈实得 10.9 vs 11.95 V，余量 1.14× vs 1.24×，两个都能用，但「取最好」应选 TBD62083A。</t>
         </is>
       </c>
     </row>

--- a/docs/06-bom/最终采购BOM-三板合并.xlsx
+++ b/docs/06-bom/最终采购BOM-三板合并.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -150,6 +150,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5272,7 +5275,6 @@
         </is>
       </c>
     </row>
-    <row r="93"/>
     <row r="94">
       <c r="C94" s="10" t="inlineStr">
         <is>
@@ -5657,7 +5659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6085,6 +6087,26 @@
       <c r="D21" s="12" t="inlineStr">
         <is>
           <t>v7 把 18 脚达林顿阵列（ULN2803A / TBD62083A）的位号从 U1 改成 U5，位置、角度、18 个脚的网络一字未改，纯改号。🔴 本 BOM 里那一行写的还是 U1，备料前必须改成 U5。🟡 待决 #84 仍未定：ULN2803A 还是 TBD62083A —— 引脚兼容，压降 1.1 V vs 44 mV，线圈实得 10.9 vs 11.95 V，余量 1.14× vs 1.24×，两个都能用，但「取最好」应选 TBD62083A。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="110" customHeight="1">
+      <c r="A22" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>MAIN-01</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>🔴 风扇端子 U11 上一只电容都没有（审图 #19 挂到现在）</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>rev23 实测：$2N135 网的全部成员就是 F5.2 + U11.2 —— 12 V 进线储能 C68/U28 在 12V 主网上，但两副带保护的输出端子 U11(经 F5)/U12(经 F6) 端子处都没有本地去耦。🔴 原理图补 100 µF/≥25 V + 100 nF 就近贴 U11。🔧 顺带：F5/F6 实画是 BSMD1206C-1100T（1.1 A 可恢复 PPTC），不是 ADR-016 文字写的「T1A 慢熔管」——意图一致（风扇不是安全相关，PTC 自恢复更合适），但采购文件措辞要统一，别订成慢熔管。🔴 U11/U12 丝印完全一样，装配文件要写死哪副接风扇。</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6653,6 +6675,62 @@
       <c r="F19" s="5" t="inlineStr">
         <is>
           <t>🔴 莲花座 `U31` 穿面板**必须用绝缘型**（外壳 = `AMP_GND`，碰机箱就给 `AGND` 加了第二个接地点，破 ADR-004）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>12 V 机箱风扇</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>散热</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>🔴 92×92×25 mm（面板放得下就 120×120×25）· 自由风量 ≥25 CFM · 转速 ≤1600 RPM · 噪声 ≤21 dB(A) · 🔴 液压/流体动压轴承（FDB/HDB，含油套筒 70 °C 只有 1.1 年寿命）· 工作温度 ≥70 °C · DC 12 V / 0.10~0.25 A · 2 线（红黑）即可，买到 3/4 线其余悬空（ADR-016 不调速常开满速）。依据：docs/01-power/风扇选型-噪声与EMI.md</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>🔴 装【进风位】不装排风：正压 + 可清洗滤棉 → 灰尘只从滤网进，保住整机爬电判据的「污染度 2」假设（待决 #86）；轴承也只见环境温度，寿命 ×5。🔴 丝网防护罩（不用冲压网板，湍流噪声高 2~4 dB）+ 橡胶减振钉。🔴 接 MAIN-01 `U11`（`.1`=GND `.2`=12 V 经 `F5`）—— `U11`/`U12` 丝印没区分，装配文件要写死。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="110" customHeight="1">
+      <c r="A21" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>进风滤网 + 滤棉</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>散热</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>配 §19 风扇尺寸的标准滤网框 + 可清洗粗孔滤棉（换气型，别用太密的）。出风口只开百叶不装风扇。</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>🔴 说明书必须写清洗周期 —— 滤网堵了正压就没了、风量掉、噪声反而涨。🟡 面板开孔要满足 IP2X（箱内 223.6 Vrms，手指不可触及带电件），图纸上写明。</t>
         </is>
       </c>
     </row>

--- a/docs/06-bom/最终采购BOM-三板合并.xlsx
+++ b/docs/06-bom/最终采购BOM-三板合并.xlsx
@@ -6021,12 +6021,12 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>🔴🔴 测量分压链下臂：806 Ω 和 576 Ω 各买 10 只</t>
+          <t>🔧 已撤销：测量分压链下臂保持 806 Ω，不买 576 Ω</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>STM32 差分 ADC 的满量程映射（码 0 对应 −V_REF/2 还是 −V_REF）一直没查实（待决 #93，要查 RM0440 或首板实测）。若是 ±V_REF/2 = ±1.45 V，则 223.6 Vrms 时电压通道占 98.3%，几乎顶格，硬件 OV 跳闸点 288 Vrms 直接削平；若是 ±2.9 V 则只占 49.1%，无需改动。✅ 补救只换这一只电阻、不动 PCB：806 Ω → 576 Ω（E96），分压比 443.9 → 620.8:1，占用降到 70.3%。🟢 两只 ±0.1% 薄膜 ≤25 ppm 电阻，几块钱 —— 各买 10 只，查实后再决定装哪只。</t>
+          <t>2026-09-23 基准段：「不再因 ±VREF/2 猜测建议换 576 Ω。实板零点、幅度、共模与削顶仍待验证。」→ 下单只买 806 Ω（±0.1% 薄膜 ≤25 ppm），不在猜测上先买第二种阻值；改为首板实测再定。🟢 软件侧的削顶检测不依赖这个常数（每个采样点查 code ≤8 或 ≥4087，软件计划 §5.5），照做即可。原始那笔账（若 FS=±V_REF/2 则 223.6 Vrms 时电压通道占 98.3%）保留在待决 #93 里备查。</t>
         </is>
       </c>
     </row>

--- a/docs/06-bom/最终采购BOM-三板合并.xlsx
+++ b/docs/06-bom/最终采购BOM-三板合并.xlsx
@@ -12,6 +12,7 @@
     <sheet name="下单必读与待核实" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="机箱件清单" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="核对记录" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="测试负载清单" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'最终采购BOM'!$A$1:$O$92</definedName>
@@ -103,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -152,6 +153,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6921,4 +6925,338 @@
   <autoFilter ref="A1:D8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>类</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>规格 / 依据</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>🔴 要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="118" customHeight="1">
+      <c r="A2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>100 Ω 无感功率电阻</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>标定 🔴必须</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>100 Ω（±5% 即可，阻值精度不重要）· ≥150 W · 🔴 无感型（厚膜/金属氧化膜/铝壳 Ayrton-Perry），普通绕线件绝对不行 · 残余电感 ≤2 µH</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>🔴🔴 相位标定（软件计划 §6.3）只能在 100 Ω 或 300 Ω 档做：夹具电感上限 100 Ω 档 2.78 µH，1 Ω 档只有 27.8 nH（物理上做不到）。同一只 0.5 µH 夹具在 100 Ω 上只加 +0.018°、在 1 Ω 上加 +1.80°。🟡 买回来用 LCR 表在 2/5/8/10 kHz 各量一次 R 和 L。兼做 100 Ω 档验收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="118" customHeight="1">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>330 nF / 630 V MKP 薄膜电容</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>标定 🟢强烈建议</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>330 nF ±5% · 630 V DC · MKP 聚丙烯 · 🔴 不能用电解（交流）、不能用 X7R 陶瓷（容值随电压温度跑 + 压电）</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>🟢 和那只 100 Ω 串起来就是相位验证夹具：2/5/8/10 kHz 分别 −67.5°/−44.0°/−31.1°/−25.7°，四个角度跨度合适。🔴 用 LCR 表量真值算理论角，判据残差 ≤0.3°。标称值不能用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="118" customHeight="1">
+      <c r="A4" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>1 Ω 并联阵列（16 只 16 Ω / 10 W）</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>验收 🔴必须</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>16 只 16 Ω 10 W 无感，每只实耗 3.1 W · 🔴 两块平行铜板上下夹住、电阻径向排布（环路面积趋零）</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>🔴 1 Ω 档 7.07 A / 50 W。并联 16 只把电感也除以 16 → 单件 50 nH 变 3.1 nH → +0.011° ✅。🔴 接线端子和线 ≥2.5 mm²，别用鳄鱼夹（接触电阻几十 mΩ 在 1 Ω 上就是几个百分点）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="118" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>3 Ω 并联阵列（12 只 36 Ω / 10 W）</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>验收 🔴必须</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>12 只 36 Ω 10 W 无感，每只实耗 4.2 W</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>🔴 3 Ω 档 4.08 A / 50 W。同上，注意引线截面积。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="118" customHeight="1">
+      <c r="A6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>10 / 30 / 300 / 1000 Ω 验收电阻</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>验收 🔴必须</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>各 1 只 · ≥150 W · 无感型 · 🔴 1000 Ω 那只耐压 ≥500 V（223.6 Vrms 峰 316 V），其余按各档 V_rms 的 2 倍</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>每档都是 50 VA。10 Ω 档 2.24 A、30 Ω 1.29 A、300 Ω 0.41 A、1000 Ω 0.22 A。100 Ω 档用第 1 项那只。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="118" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>电缆仿真阶梯 · 串臂电阻</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>仿真 🟡可选</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>0.75 Ω · ≥50 W（最坏实耗 16.7 W）· 🟢 这里可以用便宜的绕线件 —— 反正要串 175 µH，寄生电感无害</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>🟢 空心线圈自身直流电阻 0.12~0.19 Ω 本来就算在这 0.75 Ω 里 → 串阻只需补 0.56 Ω。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="118" customHeight="1">
+      <c r="A8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>电缆仿真阶梯 · 空心电感</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>仿真 🟡可选</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>175 µH · 🔴🔴 必须空心（无磁芯）· 电流 ≥5 Arms（最坏 4.72 A）· 线径 ≥1.5 mm² · 参考绕法：φ50 mm × 100 mm 长、84 圈、1.2 mm² 漆包线</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>🔴🔴 铁芯/铁氧体在 4.7 A 下一饱和，「电缆」就变成非线性元件，读数全是垃圾而且查不出原因。🔴 六只必须互相解耦：两两正交或间隔 ≥1 个线圈直径，否则互感把模型弄乱。🔴 这六只是 10 kHz/4.7 A 的磁场源，台面测试时拾音线圈要拿远。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="118" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>电缆仿真阶梯 · 节点电容</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>仿真 🟡可选</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>节点 5 只 125 nF + 两端 2 只 62 nF · 🔴 MKP 薄膜 630 V · 🔴 I_rms ≥1.5 A</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>🔴 线上最高 177 Vrms / 250 V 峰（2~10 kHz × 1~3 km × 短路/开路 全扫出来的最坏值）。10 kHz 下实际无功电流 1.39 Arms → 要看 I_rms 和 dV/dt 额定，不能只看耐压。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="118" customHeight="1">
+      <c r="A10" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>电缆仿真阶梯 · 接线柱 + 机架</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>仿真 🟡可选</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>7 个接线柱（≥10 A，间距按 400 V）+ 末端「短路/开路」切换 + 绝缘底板</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>🟢 每个节点引一个接线柱 → 一套硬件模拟 0.5/1.0/1.5/2.0/2.5/3.0 km 六种长度 × 短路/开路 = 12 种工况，不用重新焊。🟢 3 km 短路用到 10/30/100/300/1000 档、3 km 开路用到 3/10/30/100 档 → 一条阶梯扫全七档。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="118" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>🟡 预算不够时的最小仿真（1 节 Π）</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>仿真 🟢性价比最高</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>0.75 Ω + 175 µH + 2 只 62 nF = 等效 500 m</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>🟢 0.5 km 短路@10 kHz = 11.3 Ω ∠+86.0°、开路@2 kHz = 636 Ω ∠−90.0° —— 两个几乎纯电抗的极端。CC/VA 调节环（软件计划 §7）会不会在电抗性负载上振荡，纯电阻负载永远测不出来。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>